--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487579_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487579_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6995</v>
+        <v>3.8363</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8669</v>
+        <v>4.1672</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1674</v>
+        <v>-0.3309</v>
       </c>
       <c r="G2" t="n">
         <v>4.0201</v>
@@ -610,13 +610,13 @@
         <v>2.1344</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1209</v>
+        <v>0.2577</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0471</v>
+        <v>0.2532</v>
       </c>
       <c r="U2" t="n">
-        <v>0.168</v>
+        <v>0.0045</v>
       </c>
       <c r="V2" t="n">
         <v>-2.3818</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7385</v>
+        <v>1.7807</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5336</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1654</v>
+        <v>1.2472</v>
       </c>
       <c r="G3" t="n">
         <v>3.2845</v>
@@ -688,13 +688,13 @@
         <v>0.9702</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3943</v>
+        <v>0.4366</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3039</v>
+        <v>0.2644</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.1722</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2289</v>
+        <v>0.1922</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.6299</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6012</v>
+        <v>-0.4377</v>
       </c>
       <c r="G4" t="n">
         <v>-2.1841</v>
@@ -766,13 +766,13 @@
         <v>1.1642</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2189</v>
+        <v>0.1822</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3163</v>
+        <v>0.1161</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0973</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>1.2239</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. SANTAMARIA LEON</t>
+          <t>J. AYALA AYLLÓN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2718</v>
+        <v>0.0707</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7013</v>
+        <v>2.6127</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9731</v>
+        <v>-2.542</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1432</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1732</v>
+        <v>0.0305</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3163</v>
+        <v>-0.7135</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4659</v>
+        <v>2.7184</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0926</v>
+        <v>2.0638</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6267</v>
+        <v>0.6546</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6091</v>
+        <v>-3.4014</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9195</v>
+        <v>-2.0333</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6896</v>
+        <v>-1.3681</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9403</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R5" t="n">
         <v>1.9403</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5334</v>
+        <v>-0.5361</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0011</v>
+        <v>-0.2832</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5345</v>
+        <v>-0.2529</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5355</v>
+        <v>1.2898</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2343</v>
+        <v>2.1179</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7698</v>
+        <v>-0.828</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. AYALA AYLLÓN</t>
+          <t>F. SANTAMARIA LEON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3808</v>
+        <v>-0.2173</v>
       </c>
       <c r="E6" t="n">
-        <v>2.352</v>
+        <v>1.7013</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.7328</v>
+        <v>-1.9186</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.1432</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0305</v>
+        <v>1.1732</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7135</v>
+        <v>-1.3163</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7184</v>
+        <v>1.4659</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0638</v>
+        <v>2.0926</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6546</v>
+        <v>-0.6267</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.4014</v>
+        <v>-1.6091</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0333</v>
+        <v>-0.9195</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3681</v>
+        <v>-0.6896</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.9403</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>1.9403</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9877</v>
+        <v>-0.4789</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.544</v>
+        <v>0.0011</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4437</v>
+        <v>-0.48</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2898</v>
+        <v>-1.5355</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1179</v>
+        <v>0.2343</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.828</v>
+        <v>-1.7698</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7639</v>
+        <v>-0.9275</v>
       </c>
       <c r="E7" t="n">
         <v>0.164</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9278999999999999</v>
+        <v>-1.0915</v>
       </c>
       <c r="G7" t="n">
         <v>1.4249</v>
@@ -1000,13 +1000,13 @@
         <v>2.1344</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0608</v>
+        <v>-0.2243</v>
       </c>
       <c r="T7" t="n">
         <v>0.0134</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0742</v>
+        <v>-0.2378</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1579</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0731</v>
+        <v>-0.9547</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1737</v>
+        <v>0.3739</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2468</v>
+        <v>-1.3285</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1695</v>
@@ -1078,13 +1078,13 @@
         <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9035</v>
+        <v>-0.7851</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5451</v>
+        <v>-0.3449</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3584</v>
+        <v>-0.4402</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. TOLOSA OROPESA</t>
+          <t>C. BARROS CONDES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0987</v>
+        <v>-1.1007</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4412</v>
+        <v>-2.2596</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3424</v>
+        <v>1.1589</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9645</v>
+        <v>-1.1958</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3468</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3113</v>
+        <v>-1.8112</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1187</v>
+        <v>-1.1879</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0536</v>
+        <v>0.7456</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1723</v>
+        <v>-1.9335</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1542</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2933</v>
+        <v>-0.1302</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.139</v>
+        <v>0.1223</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1344</v>
+        <v>-1.1642</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5523</v>
+        <v>2.5224</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3896</v>
+        <v>-0.0393</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5298</v>
+        <v>0.0925</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1402</v>
+        <v>-0.1318</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9418</v>
+        <v>-1.2239</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-1.2239</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1838</v>
+        <v>-1.1654</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4752</v>
+        <v>-1.3751</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2914</v>
+        <v>0.2096</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1723</v>
@@ -1234,13 +1234,13 @@
         <v>0.3881</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6005</v>
+        <v>0.6188</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4856</v>
+        <v>0.5857</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1149</v>
+        <v>0.0331</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. BARROS CONDES</t>
+          <t>D. TOLOSA OROPESA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6613</v>
+        <v>-1.5631</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5204</v>
+        <v>-2.0418</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8591</v>
+        <v>0.4787</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1958</v>
+        <v>-0.9645</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.3468</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8112</v>
+        <v>-1.3113</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1879</v>
+        <v>-1.1187</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7456</v>
+        <v>0.0536</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9335</v>
+        <v>-1.1723</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.1542</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1302</v>
+        <v>0.2933</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1223</v>
+        <v>-0.139</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3582</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1642</v>
+        <v>-2.1344</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5224</v>
+        <v>1.5523</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5998</v>
+        <v>0.9253</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1683</v>
+        <v>0.9292</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4316</v>
+        <v>-0.0039</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2239</v>
+        <v>-0.9418</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X11" t="n">
         <v>-1.2239</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ GREGORIO</t>
+          <t>M. ALARCON ORTIZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.865</v>
+        <v>-2.1908</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5241</v>
+        <v>-3.1838</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3891</v>
+        <v>0.993</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.6446</v>
+        <v>-2.8514</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.856</v>
+        <v>-1.1402</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7886</v>
+        <v>-1.7112</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9162</v>
+        <v>-3.1395</v>
       </c>
       <c r="K12" t="n">
-        <v>1.4212</v>
+        <v>-1.8454</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5049</v>
+        <v>-1.2941</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5608</v>
+        <v>0.2881</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.2772</v>
+        <v>0.7052</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2836</v>
+        <v>-0.4171</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2793</v>
+        <v>-0.6096</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6079</v>
+        <v>-0.3264</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6714</v>
+        <v>-0.2832</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.6639</v>
+        <v>-0.2821</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.6639</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. ALARCON ORTIZ</t>
+          <t>S. RODRIGUEZ GREGORIO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.679</v>
+        <v>-2.7682</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6448</v>
+        <v>1.0842</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9658</v>
+        <v>-3.8524</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.8514</v>
+        <v>-1.6446</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1402</v>
+        <v>-0.856</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7112</v>
+        <v>-0.7886</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.1395</v>
+        <v>0.9162</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.8454</v>
+        <v>1.4212</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2941</v>
+        <v>-0.5049</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2881</v>
+        <v>-2.5608</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7052</v>
+        <v>-2.2772</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4171</v>
+        <v>-0.2836</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0978</v>
+        <v>0.376</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7874</v>
+        <v>0.1679</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3104</v>
+        <v>0.2081</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2821</v>
+        <v>-2.6639</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5642</v>
+        <v>-2.6639</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.310500000000001</v>
+        <v>-5.0078</v>
       </c>
       <c r="E14" t="n">
-        <v>2.103599999999999</v>
+        <v>2.4065</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.414199999999999</v>
+        <v>-7.4142</v>
       </c>
       <c r="G14" t="n">
         <v>-3.278899999999999</v>
@@ -1519,7 +1519,7 @@
         <v>-9.342700000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>9.504799999999998</v>
+        <v>9.504799999999999</v>
       </c>
       <c r="K14" t="n">
         <v>12.6466</v>
@@ -1546,13 +1546,13 @@
         <v>18.4333</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1795</v>
+        <v>0.1232999999999997</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1661</v>
+        <v>1.469</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.3456</v>
+        <v>-1.3457</v>
       </c>
       <c r="V14" t="n">
         <v>-7.6732</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>B. OJEDA OCHOA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3658</v>
+        <v>5.4277</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6347</v>
+        <v>4.9728</v>
       </c>
       <c r="F15" t="n">
-        <v>1.731</v>
+        <v>0.4549</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3723</v>
+        <v>2.7589</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9112</v>
+        <v>2.3991</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2835</v>
+        <v>0.3598</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2817</v>
+        <v>4.8811</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0381</v>
+        <v>4.2265</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2436</v>
+        <v>0.6546</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9094</v>
+        <v>-2.1221</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.9493</v>
+        <v>-1.8274</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0399</v>
+        <v>-0.2948</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7761</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1344</v>
+        <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>2.71</v>
+        <v>0.2972</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6397</v>
+        <v>0.0381</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0703</v>
+        <v>0.2591</v>
       </c>
       <c r="V15" t="n">
-        <v>3.0597</v>
+        <v>3.3418</v>
       </c>
       <c r="W15" t="n">
-        <v>3.6238</v>
+        <v>2.9641</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5642</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. OJEDA OCHOA</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9728</v>
+        <v>3.9804</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5724</v>
+        <v>2.6337</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4004</v>
+        <v>1.3467</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7589</v>
+        <v>0.3723</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3991</v>
+        <v>-0.9112</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3598</v>
+        <v>1.2835</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8811</v>
+        <v>1.2817</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2265</v>
+        <v>1.0381</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6546</v>
+        <v>0.2436</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1221</v>
+        <v>-0.9094</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8274</v>
+        <v>-1.9493</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2948</v>
+        <v>1.0399</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9702</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9403</v>
+        <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1577</v>
+        <v>1.3246</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3623</v>
+        <v>0.6387</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2046</v>
+        <v>0.6859</v>
       </c>
       <c r="V16" t="n">
-        <v>3.3418</v>
+        <v>3.0597</v>
       </c>
       <c r="W16" t="n">
-        <v>2.9641</v>
+        <v>3.6238</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3776</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4016</v>
+        <v>2.9388</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8644</v>
+        <v>2.5651</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5372</v>
+        <v>0.3737</v>
       </c>
       <c r="G17" t="n">
         <v>1.463</v>
@@ -1780,13 +1780,13 @@
         <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2436</v>
+        <v>0.2936</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9085</v>
+        <v>-0.2078</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6649</v>
+        <v>0.5014</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5642</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3045</v>
+        <v>2.2655</v>
       </c>
       <c r="E18" t="n">
-        <v>1.951</v>
+        <v>2.4515</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6466</v>
+        <v>-0.1861</v>
       </c>
       <c r="G18" t="n">
         <v>3.6679</v>
@@ -1858,13 +1858,13 @@
         <v>1.7463</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8127</v>
+        <v>0.1483</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3017</v>
+        <v>0.1988</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.511</v>
+        <v>-0.0504</v>
       </c>
       <c r="V18" t="n">
         <v>1.5537</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3647</v>
+        <v>0.516</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4113</v>
+        <v>0.2111</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0466</v>
+        <v>0.3049</v>
       </c>
       <c r="G19" t="n">
         <v>0.0736</v>
@@ -1936,13 +1936,13 @@
         <v>0.5821</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2909</v>
+        <v>-0.1396</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3645</v>
+        <v>0.1643</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6554</v>
+        <v>-0.3039</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5923</v>
+        <v>-0.5561</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7902</v>
+        <v>-0.8903</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1979</v>
+        <v>0.3342</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8123</v>
@@ -2092,13 +2092,13 @@
         <v>1.9403</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.9278</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6684</v>
+        <v>0.5683</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2232</v>
+        <v>0.3595</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6119</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. DIAZ ZARZUELA</t>
+          <t>M. TRIJUEQUE MARTIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.622</v>
+        <v>-0.9339</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0605</v>
+        <v>-0.7279</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6825</v>
+        <v>-0.206</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7289</v>
+        <v>-0.7398</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.3851</v>
+        <v>-0.0725</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6562</v>
+        <v>-0.6673</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9927</v>
+        <v>-0.6673</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9927</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0.6673</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7362</v>
+        <v>-0.0725</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3924</v>
+        <v>-0.0725</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5821</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2129</v>
+        <v>-0.194</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5175</v>
+        <v>-0.0606</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3046</v>
+        <v>-0.1335</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. TRIJUEQUE MARTIN</t>
+          <t>D. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9339</v>
+        <v>-1.193</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7279</v>
+        <v>-0.8856000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.206</v>
+        <v>-0.3074</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7398</v>
+        <v>-0.4185</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0725</v>
+        <v>0.4918</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6673</v>
+        <v>-0.9104</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6673</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.7209</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6673</v>
+        <v>-0.6267</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0725</v>
+        <v>-0.5127</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0725</v>
+        <v>-0.229</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.5821</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.194</v>
+        <v>-0.6401</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0606</v>
+        <v>-0.2633</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1335</v>
+        <v>-0.3768</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. ALMENARA SANABRIAS</t>
+          <t>F. DIAZ ZARZUELA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3176</v>
+        <v>-1.8077</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9857</v>
+        <v>-0.0406</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3319</v>
+        <v>-1.7671</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4185</v>
+        <v>-1.7289</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4918</v>
+        <v>-2.3851</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9104</v>
+        <v>0.6562</v>
       </c>
       <c r="J24" t="n">
-        <v>0.09420000000000001</v>
+        <v>-0.9927</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7209</v>
+        <v>-0.9927</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6267</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5127</v>
+        <v>-0.7362</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.229</v>
+        <v>-1.3924</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2836</v>
+        <v>0.6562</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3582</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R24" t="n">
         <v>0.5821</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7647</v>
+        <v>0.0272</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3634</v>
+        <v>0.4164</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4013</v>
+        <v>-0.3892</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2239</v>
+        <v>1.506</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.022</v>
+        <v>-1.849</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.374</v>
+        <v>-1.1738</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.648</v>
+        <v>-0.6752</v>
       </c>
       <c r="G25" t="n">
         <v>-0.2692</v>
@@ -2404,13 +2404,13 @@
         <v>0.194</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.5978</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1211</v>
+        <v>0.0791</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6496</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-1.1761</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.3446</v>
+        <v>-2.5443</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.1418</v>
+        <v>-1.6413</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.2027</v>
+        <v>-0.9029</v>
       </c>
       <c r="G26" t="n">
         <v>0.9845</v>
@@ -2482,13 +2482,13 @@
         <v>1.1642</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.2066</v>
+        <v>-0.4063</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6662</v>
+        <v>-0.1657</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5404</v>
+        <v>-0.2406</v>
       </c>
       <c r="V26" t="n">
         <v>0.5642</v>
@@ -2515,22 +2515,22 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>5.310499999999999</v>
+        <v>5.9779</v>
       </c>
       <c r="E27" t="n">
-        <v>7.414100000000001</v>
+        <v>7.4141</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.1038</v>
+        <v>-1.4363</v>
       </c>
       <c r="G27" t="n">
-        <v>3.279000000000001</v>
+        <v>3.279</v>
       </c>
       <c r="H27" t="n">
         <v>-6.063800000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>9.342700000000001</v>
+        <v>9.342700000000002</v>
       </c>
       <c r="J27" t="n">
         <v>12.784</v>
@@ -2539,10 +2539,10 @@
         <v>6.583</v>
       </c>
       <c r="L27" t="n">
-        <v>6.200999999999999</v>
+        <v>6.201000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-9.504900000000001</v>
+        <v>-9.504899999999999</v>
       </c>
       <c r="N27" t="n">
         <v>-12.6466</v>
@@ -2560,13 +2560,13 @@
         <v>12.6121</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1795999999999998</v>
+        <v>0.8468999999999997</v>
       </c>
       <c r="T27" t="n">
         <v>1.3457</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.166299999999999</v>
+        <v>-0.4989000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>7.6732</v>
